--- a/1_Data/Liang_2022_HumBrainMap/Codebook_Liang_2022_HumBrainMap_Exp1_Clean.xlsx
+++ b/1_Data/Liang_2022_HumBrainMap/Codebook_Liang_2022_HumBrainMap_Exp1_Clean.xlsx
@@ -50,6 +50,15 @@
     <t xml:space="preserve">Categorical</t>
   </si>
   <si>
+    <t xml:space="preserve">Task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task type: self-matching (shape-label matching with self/friend/stranger associations)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">self-matching</t>
+  </si>
+  <si>
     <t xml:space="preserve">Phase</t>
   </si>
   <si>
@@ -59,6 +68,15 @@
     <t xml:space="preserve">post;pre</t>
   </si>
   <si>
+    <t xml:space="preserve">Matching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whether the presented shape-label pair matches the learned association</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nonmatching;Matching</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shape</t>
   </si>
   <si>
@@ -66,24 +84,6 @@
   </si>
   <si>
     <t xml:space="preserve">stranger;self;friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task type: self-matching (shape-label matching with self/friend/stranger associations)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">self-matching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether the presented shape-label pair matches the learned association</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nonmatching;Matching</t>
   </si>
   <si>
     <t xml:space="preserve">Shape_Origin_Identity</t>
